--- a/Without LLM/Intraday_Cross_Sectional_Mean_Reversion_Without_Sentiment/live_volatiles_results_all_us.xlsx
+++ b/Without LLM/Intraday_Cross_Sectional_Mean_Reversion_Without_Sentiment/live_volatiles_results_all_us.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2483,6 +2483,160 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>$295.45</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>110.19%</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>12.67</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>5.87%</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>$437.87</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>296.14%</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>13.96</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>9.89%</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>75.00%</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
